--- a/data/Maestro_Productos_Grido.xlsx
+++ b/data/Maestro_Productos_Grido.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" r:id="R747e6d6964c24753"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aliases" sheetId="2" r:id="Rb0507c26604d42a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exclusiones" sheetId="3" r:id="R7789cc705f72416f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Explicación" sheetId="4" r:id="Rddf0d05bc2d94fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuración" sheetId="5" r:id="R3d919bdf8b4b479a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="1" r:id="Rf54aee9354e94e7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aliases" sheetId="2" r:id="R23bd639ca22b4ff2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exclusiones" sheetId="3" r:id="Rfe81082f941b40ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Explicación" sheetId="4" r:id="R1f6ff0f0134041c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuración" sheetId="5" r:id="R7c6f4ffdc11a421b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2861,13 +2861,15 @@
       <x:c r="E52" s="2" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F52" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G52" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H52" s="2"/>
+      <x:c r="F52" s="2" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="G52" s="2" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="H52" s="2" t="str">
+        <x:v>Discontinuado; excluir de pedidos y análisis nuevos</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="15" customHeight="1">
       <x:c r="A53" s="2" t="s">
@@ -3933,6 +3935,32 @@
       </x:c>
       <x:c r="H96" s="2" t="str">
         <x:v>Agregado por nuevo Mix de Ventas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>postre chocolate duo</x:v>
+      </x:c>
+      <x:c r="B97" t="n">
+        <x:v>4000998</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>PACK 6 U. POSTRE CHOCOLATE DUO GR</x:v>
+      </x:c>
+      <x:c r="D97" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E97" t="str">
+        <x:v>Producto cerrado</x:v>
+      </x:c>
+      <x:c r="F97" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="G97" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="H97" t="str">
+        <x:v>Producto nuevo. Datos de compra confirmados 27/10/2026.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3951,7 +3979,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19704c9ed6704e68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d8b255e59864489"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11041,6 +11069,60 @@
         <x:v>Preparado para venta individual</x:v>
       </x:c>
     </x:row>
+    <x:row r="271">
+      <x:c r="A271" t="str">
+        <x:v>Postre Chocolate Duo</x:v>
+      </x:c>
+      <x:c r="B271" t="str">
+        <x:v>postre chocolate duo</x:v>
+      </x:c>
+      <x:c r="C271" t="str">
+        <x:v>Producto cerrado</x:v>
+      </x:c>
+      <x:c r="D271"/>
+      <x:c r="E271" t="str">
+        <x:v>cantidad</x:v>
+      </x:c>
+      <x:c r="F271" t="str">
+        <x:v>Stock</x:v>
+      </x:c>
+      <x:c r="G271" t="str">
+        <x:v>Postres</x:v>
+      </x:c>
+      <x:c r="H271" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="I271" t="str">
+        <x:v>Código 4000998; pack x6 confirmado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" t="str">
+        <x:v>Postre Chocolate Duo</x:v>
+      </x:c>
+      <x:c r="B272" t="str">
+        <x:v>postre chocolate duo</x:v>
+      </x:c>
+      <x:c r="C272" t="str">
+        <x:v>Producto cerrado</x:v>
+      </x:c>
+      <x:c r="D272"/>
+      <x:c r="E272" t="str">
+        <x:v>cantidad</x:v>
+      </x:c>
+      <x:c r="F272" t="str">
+        <x:v>Ventas data</x:v>
+      </x:c>
+      <x:c r="G272" t="str">
+        <x:v>Postres</x:v>
+      </x:c>
+      <x:c r="H272" t="str">
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="I272" t="str">
+        <x:v>Código 4000998; pack x6 confirmado</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="H2:H216">
     <x:cfRule type="expression" dxfId="1" priority="1">
@@ -11057,7 +11139,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79ba85ba15ed49cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab9e30aff0384549"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11630,10 +11712,26 @@
         <x:v>Desactivado: omitir siempre</x:v>
       </x:c>
     </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>seleccion argentina</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>Sabor discontinuado; excluir</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>Selección Argentina 7,800 Kg - Grido</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>Sabor discontinuado; excluir</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdec8a5dd290f4616"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbd710dd84414e9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
